--- a/quality_surveys/047_digital_assessment_feedback_quality_survey--quality_surveys.xlsx
+++ b/quality_surveys/047_digital_assessment_feedback_quality_survey--quality_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -792,12 +792,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -825,12 +825,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'too_easy',_'value':_1}</t>
+          <t>too_easy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Too Easy', 'value': 1}</t>
+          <t>Too Easy</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'just_right',_'value':_2}</t>
+          <t>just_right</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Just Right', 'value': 2}</t>
+          <t>Just Right</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'too_hard',_'value':_3}</t>
+          <t>too_hard</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Too Hard', 'value': 3}</t>
+          <t>Too Hard</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'not_applicable',_'value':_4}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Not Applicable', 'value': 4}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_relevant',_'value':_1}</t>
+          <t>very_relevant</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Relevant', 'value': 1}</t>
+          <t>Very Relevant</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_relevant',_'value':_2}</t>
+          <t>somewhat_relevant</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat Relevant', 'value': 2}</t>
+          <t>Somewhat Relevant</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_relevant',_'value':_3}</t>
+          <t>not_relevant</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not Relevant', 'value': 3}</t>
+          <t>Not Relevant</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'not_applicable',_'value':_4}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Not Applicable', 'value': 4}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'excellent',_'value':_1}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Excellent', 'value': 1}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'good',_'value':_2}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Good', 'value': 2}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'fair',_'value':_3}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Fair', 'value': 3}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'poor',_'value':_4}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Poor', 'value': 4}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_poor',_'value':_5}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very Poor', 'value': 5}</t>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_1}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': 1}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_2}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': 2}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_likely',_'value':_1}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Likely', 'value': 1}</t>
+          <t>Very Likely</t>
         </is>
       </c>
     </row>
@@ -1097,12 +1097,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_likely',_'value':_2}</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat Likely', 'value': 2}</t>
+          <t>Somewhat Likely</t>
         </is>
       </c>
     </row>
@@ -1114,12 +1114,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_very_likely',_'value':_3}</t>
+          <t>not_very_likely</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not Very Likely', 'value': 3}</t>
+          <t>Not Very Likely</t>
         </is>
       </c>
     </row>
@@ -1131,29 +1131,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'not_at_all_likely',_'value':_4}</t>
+          <t>not_at_all_likely</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Not at All Likely', 'value': 4}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>question_11_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'id':_5,_'label':_'not_at_all_likely',_'value':_5}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{'id': 5, 'label': 'Not at All Likely', 'value': 5}</t>
+          <t>Not at All Likely</t>
         </is>
       </c>
     </row>
